--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
@@ -4077,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>9.698213577270508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>8.476205348968506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4135,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>5.142086029052734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>4.024070262908936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5.274232864379883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4222,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>4.659445285797119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>5.701661825180054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>12.23006749153137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>4.934741973876953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>3.751806974411011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4367,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>5.45100998878479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4396,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>5.634669065475464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4425,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>10.53570508956909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>4.244792222976685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>5.172518730163574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4.378845691680908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4541,7 +4541,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>16.30909109115601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>7.353662729263306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4599,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>3.071420907974243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4628,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>20.30801248550415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>5.424582481384277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>5.1452956199646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>5.447236776351929</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>7.164606809616089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>5.401786088943481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4802,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>8.489745140075684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>3.149577856063843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>5.73257040977478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4889,7 +4889,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>55.09426784515381</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>13.11905550956726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>5.484088897705078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>4.191458463668823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>5.801068544387817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>9.3227698802948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -5063,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>5.364220142364502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>4.836048126220703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>8.707332134246826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>12.76663875579834</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>7.797519445419312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>6.259652376174927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>7.158957958221436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5266,7 +5266,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>3.723244905471802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5295,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>12.194011926651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>9.190512895584106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>5.963657379150391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5382,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>5.287091970443726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5411,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>8.57177734375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>4.506169319152832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>12.08397698402405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>8.007830858230591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5527,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>37.86971592903137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>37.66892170906067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>4.753565073013306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>3.624024629592896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5643,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>43.27885293960571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>4.446761131286621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>36.86204695701599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5730,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>7.645975589752197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5759,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>44.15265297889709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>6.879468679428101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5817,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>20.36530327796936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>3.50294828414917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5875,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>8.149590969085693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5904,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>6.409276247024536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5933,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>80.86746215820312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5962,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>6.419903993606567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5991,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>10.55147528648376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -6020,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>3.032200574874878</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>3.885785818099976</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -6078,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>17.47556900978088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>5.151946783065796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6136,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>25.40065979957581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>9.324117422103882</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>37.5927095413208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>66.34316897392273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>4.133973360061646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6281,7 +6281,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>10.35323762893677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6310,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>7.911603450775146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>4.377741098403931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6368,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>36.44552326202393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6397,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>8.32592248916626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6426,7 +6426,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5.574077844619751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6455,7 +6455,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>18.4807710647583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6484,7 +6484,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>9.418421506881714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6513,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>3.817435264587402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6542,7 +6542,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>7.563349485397339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6571,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>5.060764789581299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6600,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>4.238087892532349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>5.811916828155518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>5.838753461837769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6687,7 +6687,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>12.48480319976807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6716,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>4.595420122146606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6745,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>5.168624877929688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6774,7 +6774,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>33.13486814498901</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6803,7 +6803,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>4.298260688781738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6832,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>3.974181652069092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6861,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>7.79002046585083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6890,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>49.2880585193634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>3.387654066085815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>27.01979660987854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>2.904808759689331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>6.02597713470459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>12.54169273376465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>55.43666505813599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -7090,7 +7090,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>10.8884015083313</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>4.977239370346069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7148,7 +7148,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>10.12367510795593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7177,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>5.392191410064697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>5.763133525848389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7235,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>2.89452600479126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7264,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>65.46663999557495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7293,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>25.85765290260315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7322,7 +7322,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>5.269294738769531</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7351,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>7.858823776245117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>6.542367219924927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7409,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>7.955543279647827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7438,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>40.32714080810547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7467,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>32.70940208435059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7496,7 +7496,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>11.17410898208618</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7525,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>61.89040088653564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7554,7 +7554,7 @@
         <v>0</v>
       </c>
       <c r="I122">
-        <v>5.325895547866821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>106.7318279743195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>60.44186234474182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7641,7 +7641,7 @@
         <v>1</v>
       </c>
       <c r="I125">
-        <v>10.04463219642639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>53.3316330909729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7699,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>14.18700242042542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>1.794819116592407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>6.995357275009155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7783,7 +7783,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>28.0286545753479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7812,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="I131">
-        <v>6.117823362350464</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7841,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="I132">
-        <v>5.574462652206421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>6.518777132034302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>77.39686965942383</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7928,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>5.294917345046997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7957,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="I136">
-        <v>7.499172449111938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7986,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>6.37869668006897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -8015,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>4.64521336555481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -8044,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>36.76757311820984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8073,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>9.441959619522095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>9.085536003112793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>7.042424201965332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8160,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>5.225767374038696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8189,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="I144">
-        <v>5.783869504928589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>4.440185070037842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8247,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>5.772104263305664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="I147">
-        <v>8.373244047164917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8305,7 +8305,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>4.871193170547485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8334,7 +8334,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>6.930055856704712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>3.564568042755127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8389,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>5.162499904632568</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8415,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>6.574753046035767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8444,7 +8444,7 @@
         <v>1</v>
       </c>
       <c r="I153">
-        <v>29.13991165161133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8473,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="I154">
-        <v>15.09733963012695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>7.576221704483032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>10.81421756744385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>17.5845959186554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8589,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="I158">
-        <v>18.84962797164917</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8618,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>14.03075981140137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>7.784537553787231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8676,7 +8676,7 @@
         <v>1</v>
       </c>
       <c r="I161">
-        <v>19.26810836791992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8705,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="I162">
-        <v>11.00267791748047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>10.9613618850708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8763,7 +8763,7 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <v>8.094591856002808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8792,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>9.25782036781311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8821,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>6.902553081512451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8850,7 +8850,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>27.52086639404297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8879,7 +8879,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>9.347595453262329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8908,7 +8908,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>15.78965497016907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8937,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="I170">
-        <v>8.251760721206665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -8966,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <v>20.80657982826233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -8995,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="I172">
-        <v>2.741729736328125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -9024,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>15.91895437240601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -9053,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>16.65881681442261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>17.2723069190979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -9108,7 +9108,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>8.330479383468628</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -9137,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="I177">
-        <v>5.460006952285767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>9.310925006866455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>16.69066739082336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -9224,7 +9224,7 @@
         <v>1</v>
       </c>
       <c r="I180">
-        <v>19.98063802719116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -9253,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>8.532566785812378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -9282,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="I182">
-        <v>7.272075653076172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>8.808575868606567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9340,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="I184">
-        <v>7.168281316757202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>6.698482513427734</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9398,7 +9398,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>17.46909809112549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9427,7 +9427,7 @@
         <v>1</v>
       </c>
       <c r="I187">
-        <v>17.60672402381897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9456,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="I188">
-        <v>8.460120677947998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9485,7 +9485,7 @@
         <v>0</v>
       </c>
       <c r="I189">
-        <v>11.74798083305359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9514,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>21.22718167304993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9543,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>6.514961004257202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9572,7 +9572,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>15.82863736152649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9601,7 +9601,7 @@
         <v>1</v>
       </c>
       <c r="I193">
-        <v>15.38987851142883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>6.674847841262817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9656,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="I195">
-        <v>8.271650314331055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9685,7 +9685,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>19.06743788719177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9714,7 +9714,7 @@
         <v>1</v>
       </c>
       <c r="I197">
-        <v>16.81735301017761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9743,7 +9743,7 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>8.148077249526978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9772,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>6.889351606369019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9801,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>9.29149866104126</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9830,7 +9830,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>15.12021970748901</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run1/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="367">
   <si>
     <t>id</t>
   </si>
@@ -2218,6 +2218,18 @@
     <t>&lt;answer&gt;(A) A. chair&lt;/answer&gt;</t>
   </si>
   <si>
+    <t>To determine which object (computer mouse, heater, door, chair) is closest to the whiteboard, I need to analyze the spatial relationships between these objects and the whiteboard across the provided frames. Since the whiteboard is visible in some frames, I will focus on the relative positions of the objects in those frames.
+First, I need to identify the whiteboard in the scene. From the frames, I can see that the whiteboard is located on a wall in one of the rooms, specifically in the frame where a desk with a chair and a computer setup is visible. The whiteboard is positioned on the wall behind the desk, which is visible in frame 2.
+Next, I need to identify the positions of the computer mouse, heater, door, and chair relative to this whiteboard. From the frames, I can see:
+1. The computer mouse is on the desk, which is in front of the whiteboard.
+2. The heater is located near the window, which is on the opposite side of the room from the whiteboard.
+3. The door is visible in frame 3, located on the far wall of the room, which is also on the opposite side of the whiteboard.
+4. The chair is located in front of the desk, which is in front of the whiteboard.
+Based on this analysis, the computer mouse is the closest to the whiteboard, as it is located on the desk, which is in front of the whiteboard. The heater and door are located on the opposite side of the room from the whiteboard, and the chair is located in front of the desk, which is in front of the whiteboard.
+Therefore, the correct answer is (A) A. computer mouse.
+&lt;answer&gt;A&lt;/answer&gt;</t>
+  </si>
+  <si>
     <t>To determine which of the objects (printer, door, power strip, exhaust fan) is closest to the trash can, we need to analyze the spatial relationships between these objects based on the provided frames. The trash can is visible in one of the frames (frame 3), and we need to identify the closest object from it.
 ### Step 1: Identify the location of the trash can
 In frame 3, the trash can is visible near the corner of the room, under the table, next to the door.
@@ -2260,6 +2272,17 @@
 The computer mouse is on the desk, which is located in front of the whiteboard. The table is also on the desk, which is located in front of the whiteboard. The monitor is on the desk, which is located in front of the whiteboard. The chair is positioned next to the desk, which is closer to the whiteboard than the chair is.
 Therefore, the computer mouse is the closest object to the whiteboard.
 &lt;answer&gt;(B) B. computer mouse&lt;/answer&gt;</t>
+  </si>
+  <si>
+    <t>To determine which object (keyboard, ceiling light, coat rack, monitor) is closest to the door, we need to analyze the spatial relationships between these objects and the door based on the provided frames. The door is visible in several frames, and we can infer its position relative to the objects.
+First, let’s identify the positions of the objects:
+- The keyboard is on the desk, near the monitor.
+- The ceiling light is visible in the ceiling area.
+- The coat rack is near the wall, next to the door.
+- The monitor is on the desk.
+From the frames, we can see that the door is located on the right side of the room, near the coat rack. The coat rack is positioned very close to the door, while the keyboard and monitor are on the desk, which is further away from the door. The ceiling light is high up and not near the door.
+Therefore, based on the spatial relationships, the coat rack is the closest to the door.
+&lt;answer&gt;C&lt;/answer&gt;</t>
   </si>
   <si>
     <t>To answer the question, we need to determine which of the objects (radiator, pillow, table, sofa) is closest to the "closet" — which we interpret as the closet door or the closet area in the room. Since we are given multiple frames from a video, we need to analyze the spatial relationships between these objects and the closet.
@@ -7467,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>0</v>
+        <v>3.775753498077393</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7571,10 +7594,10 @@
         <v>218</v>
       </c>
       <c r="E123" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="F123" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G123" t="s">
         <v>218</v>
@@ -7583,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>2.18385124206543</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7629,7 +7652,7 @@
         <v>216</v>
       </c>
       <c r="E125" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F125" t="s">
         <v>216</v>
@@ -7658,7 +7681,7 @@
         <v>218</v>
       </c>
       <c r="E126" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F126" t="s">
         <v>217</v>
@@ -7716,7 +7739,7 @@
         <v>216</v>
       </c>
       <c r="E128" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G128" t="s">
         <v>216</v>
@@ -7742,7 +7765,7 @@
         <v>215</v>
       </c>
       <c r="E129" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F129" t="s">
         <v>216</v>
@@ -7771,7 +7794,7 @@
         <v>216</v>
       </c>
       <c r="E130" t="s">
-        <v>226</v>
+        <v>316</v>
       </c>
       <c r="F130" t="s">
         <v>215</v>
@@ -7783,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>1.329896926879883</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7800,7 +7823,7 @@
         <v>215</v>
       </c>
       <c r="E131" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F131" t="s">
         <v>215</v>
@@ -7858,7 +7881,7 @@
         <v>218</v>
       </c>
       <c r="E133" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F133" t="s">
         <v>216</v>
@@ -7887,7 +7910,7 @@
         <v>217</v>
       </c>
       <c r="E134" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F134" t="s">
         <v>218</v>
@@ -7916,7 +7939,7 @@
         <v>217</v>
       </c>
       <c r="E135" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F135" t="s">
         <v>215</v>
@@ -7945,7 +7968,7 @@
         <v>217</v>
       </c>
       <c r="E136" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F136" t="s">
         <v>218</v>
@@ -7974,7 +7997,7 @@
         <v>216</v>
       </c>
       <c r="E137" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F137" t="s">
         <v>216</v>
@@ -8044,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>23.35545206069946</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -8061,7 +8084,7 @@
         <v>216</v>
       </c>
       <c r="E140" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F140" t="s">
         <v>216</v>
@@ -8119,7 +8142,7 @@
         <v>218</v>
       </c>
       <c r="E142" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F142" t="s">
         <v>216</v>
@@ -8148,7 +8171,7 @@
         <v>215</v>
       </c>
       <c r="E143" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F143" t="s">
         <v>215</v>
@@ -8206,7 +8229,7 @@
         <v>215</v>
       </c>
       <c r="E145" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F145" t="s">
         <v>216</v>
@@ -8235,7 +8258,7 @@
         <v>217</v>
       </c>
       <c r="E146" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F146" t="s">
         <v>218</v>
@@ -8293,7 +8316,7 @@
         <v>215</v>
       </c>
       <c r="E148" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F148" t="s">
         <v>215</v>
@@ -8351,7 +8374,7 @@
         <v>216</v>
       </c>
       <c r="E150" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G150" t="s">
         <v>216</v>
@@ -8377,7 +8400,7 @@
         <v>215</v>
       </c>
       <c r="E151" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F151" t="s">
         <v>217</v>
@@ -8406,7 +8429,7 @@
         <v>215</v>
       </c>
       <c r="E152" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G152" t="s">
         <v>215</v>
@@ -8432,7 +8455,7 @@
         <v>218</v>
       </c>
       <c r="E153" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F153" t="s">
         <v>218</v>
@@ -8490,7 +8513,7 @@
         <v>218</v>
       </c>
       <c r="E155" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F155" t="s">
         <v>215</v>
@@ -8519,7 +8542,7 @@
         <v>218</v>
       </c>
       <c r="E156" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F156" t="s">
         <v>215</v>
@@ -8635,7 +8658,7 @@
         <v>217</v>
       </c>
       <c r="E160" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F160" t="s">
         <v>216</v>
@@ -8664,7 +8687,7 @@
         <v>215</v>
       </c>
       <c r="E161" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F161" t="s">
         <v>215</v>
@@ -8693,7 +8716,7 @@
         <v>217</v>
       </c>
       <c r="E162" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F162" t="s">
         <v>217</v>
@@ -8722,7 +8745,7 @@
         <v>215</v>
       </c>
       <c r="E163" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F163" t="s">
         <v>215</v>
@@ -8751,7 +8774,7 @@
         <v>217</v>
       </c>
       <c r="E164" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F164" t="s">
         <v>215</v>
@@ -8780,7 +8803,7 @@
         <v>217</v>
       </c>
       <c r="E165" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F165" t="s">
         <v>215</v>
@@ -8809,7 +8832,7 @@
         <v>215</v>
       </c>
       <c r="E166" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F166" t="s">
         <v>218</v>
@@ -8867,7 +8890,7 @@
         <v>217</v>
       </c>
       <c r="E168" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F168" t="s">
         <v>217</v>
@@ -8925,7 +8948,7 @@
         <v>218</v>
       </c>
       <c r="E170" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F170" t="s">
         <v>218</v>
@@ -9012,7 +9035,7 @@
         <v>217</v>
       </c>
       <c r="E173" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F173" t="s">
         <v>218</v>
@@ -9070,7 +9093,7 @@
         <v>216</v>
       </c>
       <c r="E175" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G175" t="s">
         <v>216</v>
@@ -9096,7 +9119,7 @@
         <v>216</v>
       </c>
       <c r="E176" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F176" t="s">
         <v>215</v>
@@ -9125,7 +9148,7 @@
         <v>217</v>
       </c>
       <c r="E177" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F177" t="s">
         <v>217</v>
@@ -9154,7 +9177,7 @@
         <v>217</v>
       </c>
       <c r="E178" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F178" t="s">
         <v>215</v>
@@ -9241,7 +9264,7 @@
         <v>217</v>
       </c>
       <c r="E181" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F181" t="s">
         <v>215</v>
@@ -9270,7 +9293,7 @@
         <v>217</v>
       </c>
       <c r="E182" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F182" t="s">
         <v>217</v>
@@ -9299,7 +9322,7 @@
         <v>215</v>
       </c>
       <c r="E183" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F183" t="s">
         <v>218</v>
@@ -9328,7 +9351,7 @@
         <v>218</v>
       </c>
       <c r="E184" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F184" t="s">
         <v>217</v>
@@ -9357,7 +9380,7 @@
         <v>215</v>
       </c>
       <c r="E185" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F185" t="s">
         <v>217</v>
@@ -9386,7 +9409,7 @@
         <v>218</v>
       </c>
       <c r="E186" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F186" t="s">
         <v>217</v>
@@ -9415,7 +9438,7 @@
         <v>218</v>
       </c>
       <c r="E187" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F187" t="s">
         <v>218</v>
@@ -9444,7 +9467,7 @@
         <v>218</v>
       </c>
       <c r="E188" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F188" t="s">
         <v>218</v>
@@ -9473,7 +9496,7 @@
         <v>216</v>
       </c>
       <c r="E189" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F189" t="s">
         <v>215</v>
@@ -9531,7 +9554,7 @@
         <v>216</v>
       </c>
       <c r="E191" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F191" t="s">
         <v>217</v>
@@ -9618,7 +9641,7 @@
         <v>217</v>
       </c>
       <c r="E194" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F194" t="s">
         <v>215</v>
@@ -9647,7 +9670,7 @@
         <v>215</v>
       </c>
       <c r="E195" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G195" t="s">
         <v>215</v>
@@ -9673,7 +9696,7 @@
         <v>215</v>
       </c>
       <c r="E196" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F196" t="s">
         <v>216</v>
@@ -9702,7 +9725,7 @@
         <v>217</v>
       </c>
       <c r="E197" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F197" t="s">
         <v>217</v>
@@ -9731,7 +9754,7 @@
         <v>216</v>
       </c>
       <c r="E198" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F198" t="s">
         <v>216</v>
@@ -9760,7 +9783,7 @@
         <v>218</v>
       </c>
       <c r="E199" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F199" t="s">
         <v>215</v>
@@ -9789,7 +9812,7 @@
         <v>216</v>
       </c>
       <c r="E200" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F200" t="s">
         <v>216</v>
@@ -9818,7 +9841,7 @@
         <v>218</v>
       </c>
       <c r="E201" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F201" t="s">
         <v>218</v>
